--- a/ExcelTool/LubanTools/DataTables/Datas/ClothingData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ClothingData.xlsx
@@ -1,174 +1,181 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C823A97-9269-4C05-912F-EC5BFA29D819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17670" yWindow="4980" windowWidth="30590" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="44">
   <si>
     <t>##var</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Remark</t>
+  </si>
+  <si>
+    <t>ClothingName</t>
+  </si>
+  <si>
+    <t>ClothingIconName</t>
+  </si>
+  <si>
+    <t>ExposureValue</t>
   </si>
   <si>
     <t>##type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>long</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>TbLocalzationKeyData#sep=+</t>
+  </si>
+  <si>
+    <t>int</t>
   </si>
   <si>
     <t>##</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>long</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>服装表ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Remark</t>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>备注</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClothingIconName</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>服装名称</t>
   </si>
   <si>
     <t>服装图标</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ExposureValue</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>曝光值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClothingName</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>服装名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cloting_0.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>游泳服</t>
+  </si>
+  <si>
+    <t>Clothing+10001Name</t>
   </si>
   <si>
     <t>Cloting_1.png</t>
   </si>
   <si>
+    <t>休闲服</t>
+  </si>
+  <si>
+    <t>Clothing+10002Name</t>
+  </si>
+  <si>
     <t>Cloting_2.png</t>
   </si>
   <si>
+    <t>女仆服</t>
+  </si>
+  <si>
+    <t>Clothing+10003Name</t>
+  </si>
+  <si>
     <t>Cloting_3.png</t>
   </si>
   <si>
+    <t>修女服</t>
+  </si>
+  <si>
+    <t>Clothing+10004Name</t>
+  </si>
+  <si>
     <t>Cloting_4.png</t>
   </si>
   <si>
-    <t>游泳服</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>休闲服</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>女仆服</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>修女服</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>逆兔服</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Clothing+10001Name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Clothing+10002Name</t>
-  </si>
-  <si>
-    <t>Clothing+10003Name</t>
-  </si>
-  <si>
-    <t>Clothing+10004Name</t>
   </si>
   <si>
     <t>Clothing+10005Name</t>
   </si>
   <si>
-    <t>TbLocalzationKeyData#sep=+</t>
+    <t>Cloting_5.png</t>
+  </si>
+  <si>
+    <t>战士</t>
+  </si>
+  <si>
+    <t>Clothing+10006Name</t>
+  </si>
+  <si>
+    <t>Cloting_6.png</t>
+  </si>
+  <si>
+    <t>法师</t>
+  </si>
+  <si>
+    <t>Clothing+10007Name</t>
+  </si>
+  <si>
+    <t>Cloting_7.png</t>
+  </si>
+  <si>
+    <t>牧师</t>
+  </si>
+  <si>
+    <t>Clothing+10008Name</t>
+  </si>
+  <si>
+    <t>Cloting_8.png</t>
+  </si>
+  <si>
+    <t>游侠</t>
+  </si>
+  <si>
+    <t>Clothing+10009Name</t>
+  </si>
+  <si>
+    <t>Cloting_9.png</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -176,18 +183,362 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -195,38 +546,321 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{A7B38E6A-08B5-434F-A288-4F8779483155}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 2" xfId="49"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -275,7 +909,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
@@ -310,7 +944,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
@@ -484,177 +1118,247 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
-    <col min="3" max="3" width="11.1640625" customWidth="1"/>
-    <col min="4" max="4" width="31.75" style="4" customWidth="1"/>
+    <col min="3" max="3" width="11.1666666666667" customWidth="1"/>
+    <col min="4" max="4" width="31.75" style="1" customWidth="1"/>
     <col min="5" max="5" width="25" customWidth="1"/>
     <col min="6" max="6" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="1" ht="16.5" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>11</v>
+      <c r="E3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6">
       <c r="B4" s="1">
         <v>10001</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>26</v>
+        <v>17</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F4" s="1">
-        <v>300</v>
+        <v>200</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6">
       <c r="B5" s="1">
         <v>10002</v>
       </c>
       <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="F5" s="1">
-        <v>500</v>
+        <f t="shared" ref="F5:F12" si="0">F4+200</f>
+        <v>400</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6">
       <c r="B6" s="1">
         <v>10003</v>
       </c>
       <c r="C6" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>28</v>
+      <c r="D6" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F6" s="1">
-        <v>700</v>
+        <f t="shared" si="0"/>
+        <v>600</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6">
       <c r="B7" s="1">
         <v>10004</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>29</v>
+        <v>26</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F7" s="1">
+        <f t="shared" si="0"/>
         <v>800</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6">
       <c r="B8" s="1">
         <v>10005</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F8" s="1">
-        <v>900</v>
+        <f t="shared" si="0"/>
+        <v>1000</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B9" s="1"/>
-      <c r="E9" s="1"/>
+    <row r="9" spans="1:6">
+      <c r="B9" s="1">
+        <v>10006</v>
+      </c>
+      <c r="C9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" s="1">
+        <f t="shared" si="0"/>
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="B10" s="1">
+        <v>10007</v>
+      </c>
+      <c r="C10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" s="1">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="B11" s="1">
+        <v>10008</v>
+      </c>
+      <c r="C11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="1">
+        <f t="shared" si="0"/>
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="B12" s="1">
+        <v>10009</v>
+      </c>
+      <c r="C12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F12" s="1">
+        <f t="shared" si="0"/>
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="B13" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/ClothingData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ClothingData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4EDBED8-BCB5-462D-BD71-96BF8C3D548B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD75EEE6-C84A-4787-A288-E1B79520A34F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5470" yWindow="480" windowWidth="30590" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2280" yWindow="2280" windowWidth="26690" windowHeight="12250" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="44">
   <si>
     <t>##var</t>
   </si>
@@ -153,6 +153,21 @@
   </si>
   <si>
     <t>Cloting_0.png</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AccessoriesList</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(list#sep=+),long</t>
+  </si>
+  <si>
+    <t>配件列表</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001+10002+10003+10004</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -507,16 +522,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="11.1640625" customWidth="1"/>
     <col min="4" max="4" width="31.75" style="1" customWidth="1"/>
     <col min="5" max="5" width="25" customWidth="1"/>
-    <col min="6" max="6" width="23" customWidth="1"/>
+    <col min="6" max="6" width="38.9140625" customWidth="1"/>
+    <col min="7" max="7" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -532,11 +548,14 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -552,11 +571,14 @@
       <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -572,11 +594,14 @@
       <c r="E3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B4" s="1">
         <v>10001</v>
       </c>
@@ -589,11 +614,14 @@
       <c r="E4" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" s="1">
         <v>200</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B5" s="1">
         <v>10002</v>
       </c>
@@ -606,12 +634,15 @@
       <c r="E5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="1">
-        <f t="shared" ref="F5:F12" si="0">F4+200</f>
+      <c r="F5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G5" s="1">
+        <f t="shared" ref="G5:G12" si="0">G4+200</f>
         <v>400</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B6" s="1">
         <v>10003</v>
       </c>
@@ -624,12 +655,15 @@
       <c r="E6" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" s="1">
         <f t="shared" si="0"/>
         <v>600</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B7" s="1">
         <v>10004</v>
       </c>
@@ -642,12 +676,15 @@
       <c r="E7" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" s="1">
         <f t="shared" si="0"/>
         <v>800</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B8" s="1">
         <v>10005</v>
       </c>
@@ -660,12 +697,15 @@
       <c r="E8" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" s="1">
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B9" s="1">
         <v>10006</v>
       </c>
@@ -678,12 +718,15 @@
       <c r="E9" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" s="1">
         <f t="shared" si="0"/>
         <v>1200</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B10" s="1">
         <v>10007</v>
       </c>
@@ -696,12 +739,15 @@
       <c r="E10" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F10" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G10" s="1">
         <f t="shared" si="0"/>
         <v>1400</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B11" s="1">
         <v>10008</v>
       </c>
@@ -714,12 +760,15 @@
       <c r="E11" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" s="1">
         <f t="shared" si="0"/>
         <v>1600</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B12" s="1">
         <v>10009</v>
       </c>
@@ -732,12 +781,15 @@
       <c r="E12" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F12" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G12" s="1">
         <f t="shared" si="0"/>
         <v>1800</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B13" s="1"/>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/ClothingData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ClothingData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD75EEE6-C84A-4787-A288-E1B79520A34F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C86D848F-F08B-42D9-BFA6-EB07A0413707}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="2280" windowWidth="26690" windowHeight="12250" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3520" yWindow="1160" windowWidth="31320" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="48">
   <si>
     <t>##var</t>
   </si>
@@ -169,6 +169,20 @@
   <si>
     <t>10001+10002+10003+10004</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ClothingMinGameType</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> MinGameType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>解锁小游戏</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>熨斗小游戏</t>
   </si>
 </sst>
 </file>
@@ -232,7 +246,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -244,6 +258,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -522,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="11.1640625" customWidth="1"/>
@@ -530,9 +547,10 @@
     <col min="5" max="5" width="25" customWidth="1"/>
     <col min="6" max="6" width="38.9140625" customWidth="1"/>
     <col min="7" max="7" width="23" customWidth="1"/>
+    <col min="8" max="8" width="27.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -554,8 +572,11 @@
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H1" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -577,8 +598,11 @@
       <c r="G2" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H2" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -600,8 +624,11 @@
       <c r="G3" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H3" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B4" s="1">
         <v>10001</v>
       </c>
@@ -620,8 +647,11 @@
       <c r="G4" s="1">
         <v>200</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H4" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B5" s="1">
         <v>10002</v>
       </c>
@@ -641,8 +671,11 @@
         <f t="shared" ref="G5:G12" si="0">G4+200</f>
         <v>400</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H5" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B6" s="1">
         <v>10003</v>
       </c>
@@ -662,8 +695,11 @@
         <f t="shared" si="0"/>
         <v>600</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H6" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B7" s="1">
         <v>10004</v>
       </c>
@@ -683,8 +719,11 @@
         <f t="shared" si="0"/>
         <v>800</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H7" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B8" s="1">
         <v>10005</v>
       </c>
@@ -704,8 +743,11 @@
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H8" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B9" s="1">
         <v>10006</v>
       </c>
@@ -725,8 +767,11 @@
         <f t="shared" si="0"/>
         <v>1200</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H9" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B10" s="1">
         <v>10007</v>
       </c>
@@ -746,8 +791,11 @@
         <f t="shared" si="0"/>
         <v>1400</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H10" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B11" s="1">
         <v>10008</v>
       </c>
@@ -767,8 +815,11 @@
         <f t="shared" si="0"/>
         <v>1600</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H11" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B12" s="1">
         <v>10009</v>
       </c>
@@ -788,9 +839,13 @@
         <f t="shared" si="0"/>
         <v>1800</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H12" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B13" s="1"/>
+      <c r="H13" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/ClothingData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ClothingData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C86D848F-F08B-42D9-BFA6-EB07A0413707}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{371F9F57-55B7-49B5-8D13-15708AA941BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3520" yWindow="1160" windowWidth="31320" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="49">
   <si>
     <t>##var</t>
   </si>
@@ -183,6 +183,9 @@
   </si>
   <si>
     <t>熨斗小游戏</t>
+  </si>
+  <si>
+    <t>拼图小游戏</t>
   </si>
 </sst>
 </file>
@@ -246,7 +249,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -258,9 +261,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -572,7 +572,7 @@
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="1" t="s">
         <v>45</v>
       </c>
     </row>
@@ -624,7 +624,7 @@
       <c r="G3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="1" t="s">
         <v>46</v>
       </c>
     </row>
@@ -672,7 +672,7 @@
         <v>400</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -696,7 +696,7 @@
         <v>600</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -720,7 +720,7 @@
         <v>800</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -744,7 +744,7 @@
         <v>1000</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
@@ -768,7 +768,7 @@
         <v>1200</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
@@ -792,7 +792,7 @@
         <v>1400</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
@@ -816,7 +816,7 @@
         <v>1600</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
@@ -840,7 +840,7 @@
         <v>1800</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">

--- a/ExcelTool/LubanTools/DataTables/Datas/ClothingData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ClothingData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{371F9F57-55B7-49B5-8D13-15708AA941BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{175267D2-D18E-4150-AA09-12F20E72FB7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3520" yWindow="1160" windowWidth="31320" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5050" yWindow="2500" windowWidth="31320" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="50">
   <si>
     <t>##var</t>
   </si>
@@ -186,6 +186,9 @@
   </si>
   <si>
     <t>拼图小游戏</t>
+  </si>
+  <si>
+    <t>滴胶固化小游戏</t>
   </si>
 </sst>
 </file>
@@ -548,6 +551,7 @@
     <col min="6" max="6" width="38.9140625" customWidth="1"/>
     <col min="7" max="7" width="23" customWidth="1"/>
     <col min="8" max="8" width="27.5" customWidth="1"/>
+    <col min="9" max="9" width="21.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
@@ -696,7 +700,7 @@
         <v>600</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">

--- a/ExcelTool/LubanTools/DataTables/Datas/ClothingData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ClothingData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{175267D2-D18E-4150-AA09-12F20E72FB7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C1022BA-350B-4CF9-8E24-89A6A26A9F34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5050" yWindow="2500" windowWidth="31320" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="51">
   <si>
     <t>##var</t>
   </si>
@@ -182,13 +182,19 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>熨斗小游戏</t>
-  </si>
-  <si>
     <t>拼图小游戏</t>
   </si>
   <si>
+    <t>拼图小游戏</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>滴胶固化小游戏</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>熨斗小游戏|拼图小游戏|滴胶固化小游戏</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -550,7 +556,7 @@
     <col min="5" max="5" width="25" customWidth="1"/>
     <col min="6" max="6" width="38.9140625" customWidth="1"/>
     <col min="7" max="7" width="23" customWidth="1"/>
-    <col min="8" max="8" width="27.5" customWidth="1"/>
+    <col min="8" max="8" width="51.1640625" customWidth="1"/>
     <col min="9" max="9" width="21.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -651,8 +657,8 @@
       <c r="G4" s="1">
         <v>200</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>47</v>
+      <c r="H4" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -675,7 +681,7 @@
         <f t="shared" ref="G5:G12" si="0">G4+200</f>
         <v>400</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="4" t="s">
         <v>48</v>
       </c>
     </row>
@@ -699,7 +705,7 @@
         <f t="shared" si="0"/>
         <v>600</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" s="4" t="s">
         <v>49</v>
       </c>
     </row>
@@ -724,7 +730,7 @@
         <v>800</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -748,7 +754,7 @@
         <v>1000</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
@@ -772,7 +778,7 @@
         <v>1200</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
@@ -796,7 +802,7 @@
         <v>1400</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
@@ -820,7 +826,7 @@
         <v>1600</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
@@ -844,7 +850,7 @@
         <v>1800</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">

--- a/ExcelTool/LubanTools/DataTables/Datas/ClothingData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ClothingData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C1022BA-350B-4CF9-8E24-89A6A26A9F34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D195C78C-075B-4951-B42B-980745A173F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5050" yWindow="2500" windowWidth="31320" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4600" yWindow="2330" windowWidth="31320" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="55">
   <si>
     <t>##var</t>
   </si>
@@ -194,6 +194,22 @@
   </si>
   <si>
     <t>熨斗小游戏|拼图小游戏|滴胶固化小游戏</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>宝石Icon</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>GemIconName</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>baoshi.png</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -548,7 +564,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="11.1640625" customWidth="1"/>
@@ -560,7 +576,7 @@
     <col min="9" max="9" width="21.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -585,8 +601,11 @@
       <c r="H1" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I1" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -611,8 +630,11 @@
       <c r="H2" s="1" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I2" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -637,8 +659,11 @@
       <c r="H3" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I3" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B4" s="1">
         <v>10001</v>
       </c>
@@ -660,8 +685,11 @@
       <c r="H4" s="4" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I4" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B5" s="1">
         <v>10002</v>
       </c>
@@ -684,8 +712,11 @@
       <c r="H5" s="4" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I5" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" s="1">
         <v>10003</v>
       </c>
@@ -708,8 +739,11 @@
       <c r="H6" s="4" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I6" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B7" s="1">
         <v>10004</v>
       </c>
@@ -732,8 +766,11 @@
       <c r="H7" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I7" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B8" s="1">
         <v>10005</v>
       </c>
@@ -756,8 +793,11 @@
       <c r="H8" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I8" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B9" s="1">
         <v>10006</v>
       </c>
@@ -780,8 +820,11 @@
       <c r="H9" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I9" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B10" s="1">
         <v>10007</v>
       </c>
@@ -804,8 +847,11 @@
       <c r="H10" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I10" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B11" s="1">
         <v>10008</v>
       </c>
@@ -828,8 +874,11 @@
       <c r="H11" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I11" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B12" s="1">
         <v>10009</v>
       </c>
@@ -852,8 +901,11 @@
       <c r="H12" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I12" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B13" s="1"/>
       <c r="H13" s="1"/>
     </row>

--- a/ExcelTool/LubanTools/DataTables/Datas/ClothingData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ClothingData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D195C78C-075B-4951-B42B-980745A173F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8440EB93-191A-43CB-917A-1F4F03F7168B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4600" yWindow="2330" windowWidth="31320" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4470" yWindow="10040" windowWidth="31320" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="52">
   <si>
     <t>##var</t>
   </si>
@@ -182,21 +182,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>拼图小游戏</t>
-  </si>
-  <si>
-    <t>拼图小游戏</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>滴胶固化小游戏</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>熨斗小游戏|拼图小游戏|滴胶固化小游戏</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>string</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -211,6 +196,9 @@
   <si>
     <t>baoshi.png</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>宝石切割小游戏</t>
   </si>
 </sst>
 </file>
@@ -598,11 +586,11 @@
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="4" t="s">
         <v>45</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -631,7 +619,7 @@
         <v>44</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -660,7 +648,7 @@
         <v>46</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -683,10 +671,10 @@
         <v>200</v>
       </c>
       <c r="H4" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I4" s="4" t="s">
         <v>50</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -710,10 +698,10 @@
         <v>400</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -737,10 +725,10 @@
         <v>600</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -763,11 +751,11 @@
         <f t="shared" si="0"/>
         <v>800</v>
       </c>
-      <c r="H7" s="1" t="s">
-        <v>47</v>
+      <c r="H7" s="4" t="s">
+        <v>51</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -790,11 +778,11 @@
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
-      <c r="H8" s="1" t="s">
-        <v>47</v>
+      <c r="H8" s="4" t="s">
+        <v>51</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -817,11 +805,11 @@
         <f t="shared" si="0"/>
         <v>1200</v>
       </c>
-      <c r="H9" s="1" t="s">
-        <v>47</v>
+      <c r="H9" s="4" t="s">
+        <v>51</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
@@ -844,11 +832,11 @@
         <f t="shared" si="0"/>
         <v>1400</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>47</v>
+      <c r="H10" s="4" t="s">
+        <v>51</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -871,11 +859,11 @@
         <f t="shared" si="0"/>
         <v>1600</v>
       </c>
-      <c r="H11" s="1" t="s">
-        <v>47</v>
+      <c r="H11" s="4" t="s">
+        <v>51</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -898,11 +886,11 @@
         <f t="shared" si="0"/>
         <v>1800</v>
       </c>
-      <c r="H12" s="1" t="s">
-        <v>47</v>
+      <c r="H12" s="4" t="s">
+        <v>51</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -912,5 +900,6 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/ClothingData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ClothingData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8440EB93-191A-43CB-917A-1F4F03F7168B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59E031B8-900A-47BA-B526-F0DE8B826613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4470" yWindow="10040" windowWidth="31320" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1410" yWindow="2550" windowWidth="37150" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="55">
   <si>
     <t>##var</t>
   </si>
@@ -199,6 +199,17 @@
   </si>
   <si>
     <t>宝石切割小游戏</t>
+  </si>
+  <si>
+    <t>SmartGemPaht</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/SmartGem/GemSmart.prefab</t>
+  </si>
+  <si>
+    <t>宝石样式预制体</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -552,7 +563,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="11.1640625" customWidth="1"/>
@@ -562,9 +573,10 @@
     <col min="7" max="7" width="23" customWidth="1"/>
     <col min="8" max="8" width="51.1640625" customWidth="1"/>
     <col min="9" max="9" width="21.5" customWidth="1"/>
+    <col min="10" max="10" width="60.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -592,8 +604,11 @@
       <c r="I1" s="4" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J1" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -621,8 +636,11 @@
       <c r="I2" s="4" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J2" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -650,8 +668,11 @@
       <c r="I3" s="4" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J3" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B4" s="1">
         <v>10001</v>
       </c>
@@ -676,8 +697,11 @@
       <c r="I4" s="4" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J4" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B5" s="1">
         <v>10002</v>
       </c>
@@ -703,8 +727,11 @@
       <c r="I5" s="4" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J5" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" s="1">
         <v>10003</v>
       </c>
@@ -730,8 +757,11 @@
       <c r="I6" s="4" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J6" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B7" s="1">
         <v>10004</v>
       </c>
@@ -757,8 +787,11 @@
       <c r="I7" s="4" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J7" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B8" s="1">
         <v>10005</v>
       </c>
@@ -784,8 +817,11 @@
       <c r="I8" s="4" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J8" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="1">
         <v>10006</v>
       </c>
@@ -811,8 +847,11 @@
       <c r="I9" s="4" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J9" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B10" s="1">
         <v>10007</v>
       </c>
@@ -838,8 +877,11 @@
       <c r="I10" s="4" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J10" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B11" s="1">
         <v>10008</v>
       </c>
@@ -865,8 +907,11 @@
       <c r="I11" s="4" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J11" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B12" s="1">
         <v>10009</v>
       </c>
@@ -892,8 +937,11 @@
       <c r="I12" s="4" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J12" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B13" s="1"/>
       <c r="H13" s="1"/>
     </row>

--- a/ExcelTool/LubanTools/DataTables/Datas/ClothingData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ClothingData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59E031B8-900A-47BA-B526-F0DE8B826613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFE3A699-D49B-4805-8375-701B1B48AD67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1410" yWindow="2550" windowWidth="37150" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2500" windowWidth="37150" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -198,9 +198,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>宝石切割小游戏</t>
-  </si>
-  <si>
     <t>SmartGemPaht</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -210,6 +207,9 @@
   <si>
     <t>宝石样式预制体</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>赛车缝纫机</t>
   </si>
 </sst>
 </file>
@@ -605,7 +605,7 @@
         <v>49</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -669,7 +669,7 @@
         <v>48</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -692,13 +692,13 @@
         <v>200</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>50</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -722,13 +722,13 @@
         <v>400</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>50</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -752,13 +752,13 @@
         <v>600</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>50</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -782,13 +782,13 @@
         <v>800</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>50</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -812,13 +812,13 @@
         <v>1000</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="I8" s="4" t="s">
         <v>50</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -842,13 +842,13 @@
         <v>1200</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>50</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -872,13 +872,13 @@
         <v>1400</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>50</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -902,13 +902,13 @@
         <v>1600</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>50</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -932,13 +932,13 @@
         <v>1800</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="I12" s="4" t="s">
         <v>50</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">

--- a/ExcelTool/LubanTools/DataTables/Datas/ClothingData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ClothingData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFE3A699-D49B-4805-8375-701B1B48AD67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6A3C04B-880D-4A71-8CFE-44B1AC1B2669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="2500" windowWidth="37150" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="58">
   <si>
     <t>##var</t>
   </si>
@@ -210,6 +210,18 @@
   </si>
   <si>
     <t>赛车缝纫机</t>
+  </si>
+  <si>
+    <t>RacingTrackID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>赛车赛道ID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>long</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -273,7 +285,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -286,6 +298,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -563,7 +578,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="11.1640625" customWidth="1"/>
@@ -573,10 +588,11 @@
     <col min="7" max="7" width="23" customWidth="1"/>
     <col min="8" max="8" width="51.1640625" customWidth="1"/>
     <col min="9" max="9" width="21.5" customWidth="1"/>
-    <col min="10" max="10" width="60.6640625" customWidth="1"/>
+    <col min="10" max="10" width="34.83203125" customWidth="1"/>
+    <col min="11" max="13" width="19.9140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -607,8 +623,11 @@
       <c r="J1" s="4" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K1" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -639,8 +658,11 @@
       <c r="J2" s="4" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K2" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -671,8 +693,11 @@
       <c r="J3" s="4" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K3" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="28" x14ac:dyDescent="0.3">
       <c r="B4" s="1">
         <v>10001</v>
       </c>
@@ -697,11 +722,14 @@
       <c r="I4" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J4" s="5" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K4" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="28" x14ac:dyDescent="0.3">
       <c r="B5" s="1">
         <v>10002</v>
       </c>
@@ -727,11 +755,14 @@
       <c r="I5" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" s="5" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="28" x14ac:dyDescent="0.3">
       <c r="B6" s="1">
         <v>10003</v>
       </c>
@@ -757,11 +788,14 @@
       <c r="I6" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="J6" s="5" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="28" x14ac:dyDescent="0.3">
       <c r="B7" s="1">
         <v>10004</v>
       </c>
@@ -787,11 +821,14 @@
       <c r="I7" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="J7" s="5" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K7" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="28" x14ac:dyDescent="0.3">
       <c r="B8" s="1">
         <v>10005</v>
       </c>
@@ -817,11 +854,14 @@
       <c r="I8" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="J8" s="5" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K8" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="28" x14ac:dyDescent="0.3">
       <c r="B9" s="1">
         <v>10006</v>
       </c>
@@ -847,11 +887,14 @@
       <c r="I9" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="J9" s="5" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K9" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="28" x14ac:dyDescent="0.3">
       <c r="B10" s="1">
         <v>10007</v>
       </c>
@@ -877,11 +920,14 @@
       <c r="I10" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="J10" s="5" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K10" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="28" x14ac:dyDescent="0.3">
       <c r="B11" s="1">
         <v>10008</v>
       </c>
@@ -907,11 +953,14 @@
       <c r="I11" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="J11" s="5" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K11" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="28" x14ac:dyDescent="0.3">
       <c r="B12" s="1">
         <v>10009</v>
       </c>
@@ -937,11 +986,14 @@
       <c r="I12" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="J12" s="5" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K12" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B13" s="1"/>
       <c r="H13" s="1"/>
     </row>

--- a/ExcelTool/LubanTools/DataTables/Datas/ClothingData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ClothingData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6A3C04B-880D-4A71-8CFE-44B1AC1B2669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62EC659C-9E03-49EC-800A-8970F0BFEDFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="2500" windowWidth="37150" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -209,9 +209,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>赛车缝纫机</t>
-  </si>
-  <si>
     <t>RacingTrackID</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -222,6 +219,9 @@
   <si>
     <t>long</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>服装上身</t>
   </si>
 </sst>
 </file>
@@ -624,7 +624,7 @@
         <v>51</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -659,7 +659,7 @@
         <v>47</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -694,7 +694,7 @@
         <v>53</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="28" x14ac:dyDescent="0.3">
@@ -717,7 +717,7 @@
         <v>200</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>50</v>
@@ -750,7 +750,7 @@
         <v>400</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>50</v>
@@ -783,7 +783,7 @@
         <v>600</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>50</v>
@@ -816,7 +816,7 @@
         <v>800</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>50</v>
@@ -849,7 +849,7 @@
         <v>1000</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I8" s="4" t="s">
         <v>50</v>
@@ -882,7 +882,7 @@
         <v>1200</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>50</v>
@@ -915,7 +915,7 @@
         <v>1400</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>50</v>
@@ -948,7 +948,7 @@
         <v>1600</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>50</v>
@@ -981,7 +981,7 @@
         <v>1800</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I12" s="4" t="s">
         <v>50</v>

--- a/ExcelTool/LubanTools/DataTables/Datas/ClothingData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ClothingData.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\text\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6A3C04B-880D-4A71-8CFE-44B1AC1B2669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2500" windowWidth="37150" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="56">
   <si>
     <t>##var</t>
   </si>
@@ -50,9 +49,24 @@
     <t>ClothingIconName</t>
   </si>
   <si>
+    <t>AccessoriesList</t>
+  </si>
+  <si>
     <t>ExposureValue</t>
   </si>
   <si>
+    <t xml:space="preserve"> MinGameType</t>
+  </si>
+  <si>
+    <t>GemIconName</t>
+  </si>
+  <si>
+    <t>SmartGemPaht</t>
+  </si>
+  <si>
+    <t>RacingTrackID</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -65,9 +79,15 @@
     <t>TbLocalzationKeyData#sep=+</t>
   </si>
   <si>
+    <t>(list#sep=+),long</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
+    <t>ClothingMinGameType</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
@@ -83,51 +103,81 @@
     <t>服装图标</t>
   </si>
   <si>
+    <t>配件列表</t>
+  </si>
+  <si>
     <t>曝光值</t>
   </si>
   <si>
+    <t>解锁小游戏</t>
+  </si>
+  <si>
+    <t>宝石Icon</t>
+  </si>
+  <si>
+    <t>宝石样式预制体</t>
+  </si>
+  <si>
+    <t>赛车赛道ID</t>
+  </si>
+  <si>
     <t>游泳服</t>
   </si>
   <si>
     <t>Clothing+10001Name</t>
   </si>
   <si>
+    <t>Cloting_0.png</t>
+  </si>
+  <si>
+    <t>10001+10002+10003+10004</t>
+  </si>
+  <si>
+    <t>刺绣填色</t>
+  </si>
+  <si>
+    <t>baoshi.png</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/SmartGem/GemSmart.prefab</t>
+  </si>
+  <si>
+    <t>休闲服</t>
+  </si>
+  <si>
+    <t>Clothing+10002Name</t>
+  </si>
+  <si>
     <t>Cloting_1.png</t>
   </si>
   <si>
-    <t>休闲服</t>
-  </si>
-  <si>
-    <t>Clothing+10002Name</t>
+    <t>女仆服</t>
+  </si>
+  <si>
+    <t>Clothing+10003Name</t>
   </si>
   <si>
     <t>Cloting_2.png</t>
   </si>
   <si>
-    <t>女仆服</t>
-  </si>
-  <si>
-    <t>Clothing+10003Name</t>
+    <t>修女服</t>
+  </si>
+  <si>
+    <t>Clothing+10004Name</t>
   </si>
   <si>
     <t>Cloting_3.png</t>
   </si>
   <si>
-    <t>修女服</t>
-  </si>
-  <si>
-    <t>Clothing+10004Name</t>
+    <t>逆兔服</t>
+  </si>
+  <si>
+    <t>Clothing+10005Name</t>
   </si>
   <si>
     <t>Cloting_4.png</t>
   </si>
   <si>
-    <t>逆兔服</t>
-  </si>
-  <si>
-    <t>Clothing+10005Name</t>
-  </si>
-  <si>
     <t>战士</t>
   </si>
   <si>
@@ -150,85 +200,19 @@
   </si>
   <si>
     <t>Clothing+10009Name</t>
-  </si>
-  <si>
-    <t>Cloting_0.png</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>AccessoriesList</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>(list#sep=+),long</t>
-  </si>
-  <si>
-    <t>配件列表</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>10001+10002+10003+10004</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClothingMinGameType</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MinGameType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>解锁小游戏</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>宝石Icon</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>GemIconName</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>baoshi.png</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SmartGemPaht</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/AddressableAssets/Remote/Prefabs/SmartGem/GemSmart.prefab</t>
-  </si>
-  <si>
-    <t>宝石样式预制体</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>赛车缝纫机</t>
-  </si>
-  <si>
-    <t>RacingTrackID</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>赛车赛道ID</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>long</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -240,39 +224,355 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -280,41 +580,327 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 2" xfId="49"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -572,27 +1158,27 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="3" max="3" width="11.1640625" customWidth="1"/>
+    <col min="3" max="3" width="11.1666666666667" customWidth="1"/>
     <col min="4" max="4" width="31.75" style="1" customWidth="1"/>
     <col min="5" max="5" width="25" customWidth="1"/>
-    <col min="6" max="6" width="38.9140625" customWidth="1"/>
+    <col min="6" max="6" width="38.9166666666667" customWidth="1"/>
     <col min="7" max="7" width="23" customWidth="1"/>
-    <col min="8" max="8" width="51.1640625" customWidth="1"/>
+    <col min="8" max="8" width="51.1666666666667" customWidth="1"/>
     <col min="9" max="9" width="21.5" customWidth="1"/>
-    <col min="10" max="10" width="34.83203125" customWidth="1"/>
-    <col min="11" max="13" width="19.9140625" customWidth="1"/>
+    <col min="10" max="10" width="34.8333333333333" customWidth="1"/>
+    <col min="11" max="13" width="19.9166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="1" ht="16.5" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -609,397 +1195,397 @@
         <v>4</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>55</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>57</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="28" x14ac:dyDescent="0.3">
+    <row r="4" ht="28" spans="1:11">
       <c r="B4" s="1">
         <v>10001</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="G4" s="1">
         <v>200</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="K4" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="28" x14ac:dyDescent="0.3">
+    <row r="5" ht="28" spans="1:11">
       <c r="B5" s="1">
         <v>10002</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="G5" s="1">
         <f t="shared" ref="G5:G12" si="0">G4+200</f>
         <v>400</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="K5" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="28" x14ac:dyDescent="0.3">
+    <row r="6" ht="28" spans="1:11">
       <c r="B6" s="1">
         <v>10003</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="G6" s="1">
         <f t="shared" si="0"/>
         <v>600</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="K6" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="28" x14ac:dyDescent="0.3">
+    <row r="7" ht="28" spans="1:11">
       <c r="B7" s="1">
         <v>10004</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="G7" s="1">
         <f t="shared" si="0"/>
         <v>800</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="K7" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="28" x14ac:dyDescent="0.3">
+    <row r="8" ht="28" spans="1:11">
       <c r="B8" s="1">
         <v>10005</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="G8" s="1">
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="K8" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="28" x14ac:dyDescent="0.3">
+    <row r="9" ht="28" spans="1:11">
       <c r="B9" s="1">
         <v>10006</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>43</v>
       </c>
       <c r="G9" s="1">
         <f t="shared" si="0"/>
         <v>1200</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="K9" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="28" x14ac:dyDescent="0.3">
+    <row r="10" ht="28" spans="1:11">
       <c r="B10" s="1">
         <v>10007</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="G10" s="1">
         <f t="shared" si="0"/>
         <v>1400</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="K10" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="28" x14ac:dyDescent="0.3">
+    <row r="11" ht="28" spans="1:11">
       <c r="B11" s="1">
         <v>10008</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="G11" s="1">
         <f t="shared" si="0"/>
         <v>1600</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="K11" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="28" x14ac:dyDescent="0.3">
+    <row r="12" ht="28" spans="1:11">
       <c r="B12" s="1">
         <v>10009</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="G12" s="1">
         <f t="shared" si="0"/>
         <v>1800</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="K12" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11">
       <c r="B13" s="1"/>
       <c r="H13" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/ClothingData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ClothingData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62EC659C-9E03-49EC-800A-8970F0BFEDFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5245ED86-FD93-4D76-A32D-386493D1A955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2500" windowWidth="37150" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13790" yWindow="3090" windowWidth="37160" windowHeight="17840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -167,10 +167,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>10001+10002+10003+10004</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>ClothingMinGameType</t>
   </si>
   <si>
@@ -222,6 +218,10 @@
   </si>
   <si>
     <t>服装上身</t>
+  </si>
+  <si>
+    <t>10000+10001+10002+10003+10004+10005</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -615,16 +615,16 @@
         <v>5</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -650,16 +650,16 @@
         <v>10</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -685,16 +685,16 @@
         <v>16</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="28" x14ac:dyDescent="0.3">
@@ -711,19 +711,19 @@
         <v>39</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="G4" s="1">
         <v>200</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K4" s="1">
         <v>1</v>
@@ -743,20 +743,20 @@
         <v>19</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="G5" s="1">
         <f t="shared" ref="G5:G12" si="0">G4+200</f>
         <v>400</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K5" s="1">
         <v>1</v>
@@ -776,20 +776,20 @@
         <v>22</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="G6" s="1">
         <f t="shared" si="0"/>
         <v>600</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K6" s="1">
         <v>1</v>
@@ -809,20 +809,20 @@
         <v>25</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="G7" s="1">
         <f t="shared" si="0"/>
         <v>800</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K7" s="1">
         <v>1</v>
@@ -842,20 +842,20 @@
         <v>28</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="G8" s="1">
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K8" s="1">
         <v>1</v>
@@ -875,20 +875,20 @@
         <v>28</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="G9" s="1">
         <f t="shared" si="0"/>
         <v>1200</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K9" s="1">
         <v>1</v>
@@ -908,20 +908,20 @@
         <v>28</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="G10" s="1">
         <f t="shared" si="0"/>
         <v>1400</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K10" s="1">
         <v>1</v>
@@ -941,20 +941,20 @@
         <v>28</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="G11" s="1">
         <f t="shared" si="0"/>
         <v>1600</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K11" s="1">
         <v>1</v>
@@ -974,20 +974,20 @@
         <v>28</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="G12" s="1">
         <f t="shared" si="0"/>
         <v>1800</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K12" s="1">
         <v>1</v>

--- a/ExcelTool/LubanTools/DataTables/Datas/ClothingData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ClothingData.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\text\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5245ED86-FD93-4D76-A32D-386493D1A955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13790" yWindow="3090" windowWidth="37160" windowHeight="17840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="62">
   <si>
     <t>##var</t>
   </si>
@@ -50,9 +49,24 @@
     <t>ClothingIconName</t>
   </si>
   <si>
+    <t>AccessoriesList</t>
+  </si>
+  <si>
     <t>ExposureValue</t>
   </si>
   <si>
+    <t xml:space="preserve"> MinGameType</t>
+  </si>
+  <si>
+    <t>GemIconName</t>
+  </si>
+  <si>
+    <t>SmartGemPaht</t>
+  </si>
+  <si>
+    <t>RacingTrackID</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -65,9 +79,15 @@
     <t>TbLocalzationKeyData#sep=+</t>
   </si>
   <si>
+    <t>(list#sep=+),long</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
+    <t>ClothingMinGameType</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
@@ -83,49 +103,91 @@
     <t>服装图标</t>
   </si>
   <si>
+    <t>配件列表</t>
+  </si>
+  <si>
     <t>曝光值</t>
   </si>
   <si>
+    <t>解锁小游戏</t>
+  </si>
+  <si>
+    <t>宝石Icon</t>
+  </si>
+  <si>
+    <t>宝石样式预制体</t>
+  </si>
+  <si>
+    <t>赛车赛道ID</t>
+  </si>
+  <si>
     <t>游泳服</t>
   </si>
   <si>
     <t>Clothing+10001Name</t>
   </si>
   <si>
+    <t>Cloting_0.png</t>
+  </si>
+  <si>
+    <t>10000+10001+10002+10003+10004+10005</t>
+  </si>
+  <si>
+    <t>熨斗小游戏|拼图小游戏|滴胶固化小游戏|服装上身</t>
+  </si>
+  <si>
+    <t>baoshi.png</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/SmartGem/GemSmart.prefab</t>
+  </si>
+  <si>
+    <t>休闲服</t>
+  </si>
+  <si>
+    <t>Clothing+10002Name</t>
+  </si>
+  <si>
     <t>Cloting_1.png</t>
   </si>
   <si>
-    <t>休闲服</t>
-  </si>
-  <si>
-    <t>Clothing+10002Name</t>
+    <t>拼图小游戏|滴胶固化小游戏|宝石切割小游戏|服装上身</t>
+  </si>
+  <si>
+    <t>女仆服</t>
+  </si>
+  <si>
+    <t>Clothing+10003Name</t>
   </si>
   <si>
     <t>Cloting_2.png</t>
   </si>
   <si>
-    <t>女仆服</t>
-  </si>
-  <si>
-    <t>Clothing+10003Name</t>
+    <t>滴胶固化小游戏|宝石切割小游戏|喷漆小游戏|服装上身</t>
+  </si>
+  <si>
+    <t>修女服</t>
+  </si>
+  <si>
+    <t>Clothing+10004Name</t>
   </si>
   <si>
     <t>Cloting_3.png</t>
   </si>
   <si>
-    <t>修女服</t>
-  </si>
-  <si>
-    <t>Clothing+10004Name</t>
+    <t>宝石切割小游戏|喷漆小游戏|赛车缝纫机|服装上身</t>
+  </si>
+  <si>
+    <t>逆兔服</t>
+  </si>
+  <si>
+    <t>Clothing+10005Name</t>
   </si>
   <si>
     <t>Cloting_4.png</t>
   </si>
   <si>
-    <t>逆兔服</t>
-  </si>
-  <si>
-    <t>Clothing+10005Name</t>
+    <t>喷漆小游戏|赛车缝纫机|刺绣填色|服装上身</t>
   </si>
   <si>
     <t>战士</t>
@@ -134,12 +196,18 @@
     <t>Clothing+10006Name</t>
   </si>
   <si>
+    <t>赛车缝纫机|刺绣填色|熨斗小游戏|服装上身</t>
+  </si>
+  <si>
     <t>法师</t>
   </si>
   <si>
     <t>Clothing+10007Name</t>
   </si>
   <si>
+    <t>刺绣填色|熨斗小游戏|拼图小游戏|服装上身</t>
+  </si>
+  <si>
     <t>牧师</t>
   </si>
   <si>
@@ -150,85 +218,19 @@
   </si>
   <si>
     <t>Clothing+10009Name</t>
-  </si>
-  <si>
-    <t>Cloting_0.png</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>AccessoriesList</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>(list#sep=+),long</t>
-  </si>
-  <si>
-    <t>配件列表</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClothingMinGameType</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MinGameType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>解锁小游戏</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>宝石Icon</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>GemIconName</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>baoshi.png</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SmartGemPaht</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/AddressableAssets/Remote/Prefabs/SmartGem/GemSmart.prefab</t>
-  </si>
-  <si>
-    <t>宝石样式预制体</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>RacingTrackID</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>赛车赛道ID</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>long</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>服装上身</t>
-  </si>
-  <si>
-    <t>10000+10001+10002+10003+10004+10005</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -240,39 +242,355 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -280,41 +598,327 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 2" xfId="49"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -572,27 +1176,27 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="3" max="3" width="11.1640625" customWidth="1"/>
+    <col min="3" max="3" width="11.1666666666667" customWidth="1"/>
     <col min="4" max="4" width="31.75" style="1" customWidth="1"/>
     <col min="5" max="5" width="25" customWidth="1"/>
-    <col min="6" max="6" width="38.9140625" customWidth="1"/>
+    <col min="6" max="6" width="38.9166666666667" customWidth="1"/>
     <col min="7" max="7" width="23" customWidth="1"/>
-    <col min="8" max="8" width="51.1640625" customWidth="1"/>
+    <col min="8" max="8" width="51.1666666666667" customWidth="1"/>
     <col min="9" max="9" width="21.5" customWidth="1"/>
-    <col min="10" max="10" width="34.83203125" customWidth="1"/>
-    <col min="11" max="13" width="19.9140625" customWidth="1"/>
+    <col min="10" max="10" width="34.8333333333333" customWidth="1"/>
+    <col min="11" max="13" width="19.9166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="1" ht="16.5" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -609,397 +1213,397 @@
         <v>4</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>55</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="28" x14ac:dyDescent="0.3">
+    <row r="4" ht="28" spans="1:11">
       <c r="B4" s="1">
         <v>10001</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="G4" s="1">
         <v>200</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="K4" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="28" x14ac:dyDescent="0.3">
+    <row r="5" ht="28" spans="1:11">
       <c r="B5" s="1">
         <v>10002</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="G5" s="1">
         <f t="shared" ref="G5:G12" si="0">G4+200</f>
         <v>400</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="K5" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="28" x14ac:dyDescent="0.3">
+    <row r="6" ht="28" spans="1:11">
       <c r="B6" s="1">
         <v>10003</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="G6" s="1">
         <f t="shared" si="0"/>
         <v>600</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="K6" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="28" x14ac:dyDescent="0.3">
+    <row r="7" ht="28" spans="1:11">
       <c r="B7" s="1">
         <v>10004</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="G7" s="1">
         <f t="shared" si="0"/>
         <v>800</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="K7" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="28" x14ac:dyDescent="0.3">
+    <row r="8" ht="28" spans="1:11">
       <c r="B8" s="1">
         <v>10005</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="G8" s="1">
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="K8" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="28" x14ac:dyDescent="0.3">
+    <row r="9" ht="28" spans="1:11">
       <c r="B9" s="1">
         <v>10006</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>57</v>
       </c>
       <c r="G9" s="1">
         <f t="shared" si="0"/>
         <v>1200</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="K9" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="28" x14ac:dyDescent="0.3">
+    <row r="10" ht="28" spans="1:11">
       <c r="B10" s="1">
         <v>10007</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="G10" s="1">
         <f t="shared" si="0"/>
         <v>1400</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="K10" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="28" x14ac:dyDescent="0.3">
+    <row r="11" ht="28" spans="1:11">
       <c r="B11" s="1">
         <v>10008</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="G11" s="1">
         <f t="shared" si="0"/>
         <v>1600</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="K11" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="28" x14ac:dyDescent="0.3">
+    <row r="12" ht="28" spans="1:11">
       <c r="B12" s="1">
         <v>10009</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="G12" s="1">
         <f t="shared" si="0"/>
         <v>1800</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="K12" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11">
       <c r="B13" s="1"/>
       <c r="H13" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/ClothingData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ClothingData.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="56">
   <si>
     <t>##var</t>
   </si>
@@ -133,7 +133,7 @@
     <t>10000+10001+10002+10003+10004+10005</t>
   </si>
   <si>
-    <t>熨斗小游戏|拼图小游戏|滴胶固化小游戏|服装上身</t>
+    <t>服装上身</t>
   </si>
   <si>
     <t>baoshi.png</t>
@@ -151,9 +151,6 @@
     <t>Cloting_1.png</t>
   </si>
   <si>
-    <t>拼图小游戏|滴胶固化小游戏|宝石切割小游戏|服装上身</t>
-  </si>
-  <si>
     <t>女仆服</t>
   </si>
   <si>
@@ -163,9 +160,6 @@
     <t>Cloting_2.png</t>
   </si>
   <si>
-    <t>滴胶固化小游戏|宝石切割小游戏|喷漆小游戏|服装上身</t>
-  </si>
-  <si>
     <t>修女服</t>
   </si>
   <si>
@@ -175,9 +169,6 @@
     <t>Cloting_3.png</t>
   </si>
   <si>
-    <t>宝石切割小游戏|喷漆小游戏|赛车缝纫机|服装上身</t>
-  </si>
-  <si>
     <t>逆兔服</t>
   </si>
   <si>
@@ -187,25 +178,16 @@
     <t>Cloting_4.png</t>
   </si>
   <si>
-    <t>喷漆小游戏|赛车缝纫机|刺绣填色|服装上身</t>
-  </si>
-  <si>
     <t>战士</t>
   </si>
   <si>
     <t>Clothing+10006Name</t>
   </si>
   <si>
-    <t>赛车缝纫机|刺绣填色|熨斗小游戏|服装上身</t>
-  </si>
-  <si>
     <t>法师</t>
   </si>
   <si>
     <t>Clothing+10007Name</t>
-  </si>
-  <si>
-    <t>刺绣填色|熨斗小游戏|拼图小游戏|服装上身</t>
   </si>
   <si>
     <t>牧师</t>
@@ -230,7 +212,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -243,13 +225,6 @@
       <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -714,133 +689,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -856,7 +831,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1354,7 +1329,7 @@
         <v>400</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>34</v>
@@ -1371,13 +1346,13 @@
         <v>10003</v>
       </c>
       <c r="C6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>32</v>
@@ -1387,7 +1362,7 @@
         <v>600</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>34</v>
@@ -1404,13 +1379,13 @@
         <v>10004</v>
       </c>
       <c r="C7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>46</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>32</v>
@@ -1420,7 +1395,7 @@
         <v>800</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>34</v>
@@ -1437,13 +1412,13 @@
         <v>10005</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>32</v>
@@ -1453,7 +1428,7 @@
         <v>1000</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="I8" s="4" t="s">
         <v>34</v>
@@ -1470,13 +1445,13 @@
         <v>10006</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>32</v>
@@ -1486,7 +1461,7 @@
         <v>1200</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>34</v>
@@ -1503,13 +1478,13 @@
         <v>10007</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>32</v>
@@ -1519,7 +1494,7 @@
         <v>1400</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>34</v>
@@ -1536,13 +1511,13 @@
         <v>10008</v>
       </c>
       <c r="C11" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>32</v>
@@ -1569,13 +1544,13 @@
         <v>10009</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>32</v>
@@ -1585,7 +1560,7 @@
         <v>1800</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="I12" s="4" t="s">
         <v>34</v>

--- a/ExcelTool/LubanTools/DataTables/Datas/ClothingData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ClothingData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D56BB3F-968A-41F8-8178-35541F356134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EC0EC6B-BCC4-4871-B506-D76C36510E34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="380" windowWidth="37160" windowHeight="17840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="3040" windowWidth="37160" windowHeight="17840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="56">
   <si>
     <t>##var</t>
   </si>
@@ -189,13 +189,29 @@
   </si>
   <si>
     <t>Clothing+10009Name</t>
+  </si>
+  <si>
+    <t>CharacterClothingSlotPath</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>服装装配预制体</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/CharacterClothingSlot/10001.prefab</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -228,6 +244,14 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -250,7 +274,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -266,6 +290,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -543,7 +570,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="11.1640625" customWidth="1"/>
@@ -553,10 +580,12 @@
     <col min="7" max="7" width="23" customWidth="1"/>
     <col min="8" max="8" width="21.5" customWidth="1"/>
     <col min="9" max="9" width="34.83203125" customWidth="1"/>
-    <col min="10" max="12" width="19.9140625" customWidth="1"/>
+    <col min="10" max="10" width="19.9140625" customWidth="1"/>
+    <col min="11" max="11" width="68.4140625" customWidth="1"/>
+    <col min="12" max="12" width="19.9140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -587,8 +616,11 @@
       <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K1" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -619,8 +651,11 @@
       <c r="J2" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K2" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -651,8 +686,11 @@
       <c r="J3" s="4" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" ht="28" x14ac:dyDescent="0.3">
+      <c r="K3" s="6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="28" x14ac:dyDescent="0.3">
       <c r="B4" s="1">
         <v>10001</v>
       </c>
@@ -680,8 +718,11 @@
       <c r="J4" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" ht="28" x14ac:dyDescent="0.3">
+      <c r="K4" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="28" x14ac:dyDescent="0.3">
       <c r="B5" s="1">
         <v>10002</v>
       </c>
@@ -710,8 +751,11 @@
       <c r="J5" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="28" x14ac:dyDescent="0.3">
+      <c r="K5" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="28" x14ac:dyDescent="0.3">
       <c r="B6" s="1">
         <v>10003</v>
       </c>
@@ -740,8 +784,11 @@
       <c r="J6" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" ht="28" x14ac:dyDescent="0.3">
+      <c r="K6" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="28" x14ac:dyDescent="0.3">
       <c r="B7" s="1">
         <v>10004</v>
       </c>
@@ -770,8 +817,11 @@
       <c r="J7" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" ht="28" x14ac:dyDescent="0.3">
+      <c r="K7" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="28" x14ac:dyDescent="0.3">
       <c r="B8" s="1">
         <v>10005</v>
       </c>
@@ -800,8 +850,11 @@
       <c r="J8" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" ht="28" x14ac:dyDescent="0.3">
+      <c r="K8" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="28" x14ac:dyDescent="0.3">
       <c r="B9" s="1">
         <v>10006</v>
       </c>
@@ -830,8 +883,11 @@
       <c r="J9" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" ht="28" x14ac:dyDescent="0.3">
+      <c r="K9" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="28" x14ac:dyDescent="0.3">
       <c r="B10" s="1">
         <v>10007</v>
       </c>
@@ -860,8 +916,11 @@
       <c r="J10" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" ht="28" x14ac:dyDescent="0.3">
+      <c r="K10" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="28" x14ac:dyDescent="0.3">
       <c r="B11" s="1">
         <v>10008</v>
       </c>
@@ -890,8 +949,11 @@
       <c r="J11" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" ht="28" x14ac:dyDescent="0.3">
+      <c r="K11" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="28" x14ac:dyDescent="0.3">
       <c r="B12" s="1">
         <v>10009</v>
       </c>
@@ -920,8 +982,11 @@
       <c r="J12" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K12" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B13" s="1"/>
     </row>
   </sheetData>
